--- a/public/uploads/file/2025-11-30/2025Bcsk2bUysZ1764494891.xlsx
+++ b/public/uploads/file/2025-11-30/2025Bcsk2bUysZ1764494891.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14400" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>礼盒5kg*1</t>
   </si>
   <si>
-    <t>964250072459739000</t>
+    <t>964250072459739137</t>
   </si>
   <si>
     <t>刘冬冬</t>
@@ -82,7 +82,7 @@
     <t>胡姬花食用油金龙鱼面粉</t>
   </si>
   <si>
-    <t>964250072434049000</t>
+    <t>964250072434049024</t>
   </si>
   <si>
     <t>5kg面粉+5L食用油</t>
@@ -94,7 +94,7 @@
     <t>机长箱</t>
   </si>
   <si>
-    <t>964250068139081000</t>
+    <t>964250068139081728</t>
   </si>
   <si>
     <t>深灰色/16寸</t>
@@ -782,7 +782,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -819,14 +819,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1193,13 +1187,13 @@
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="10">
@@ -1225,13 +1219,13 @@
       <c r="A3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="10">
@@ -1254,16 +1248,16 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:10">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="10">
